--- a/duoki_editor/resources/data/blank/商店-道具组合-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/商店-道具组合-1-blank.xlsx
@@ -106,13 +106,13 @@
     <t>{user_name}，我们赶紧开始制造道具吧！</t>
   </si>
   <si>
-    <t>{user_name}，`请先把[球|气球|娃娃|玩具车|糖果|巧克力|饼干|汉堡包|披萨|意大利面|酸奶|可乐|果汁|柠檬汁]放在咕噜咕噜魔法盒上，激发它魔法力量吧！`</t>
-  </si>
-  <si>
-    <t>{user_name}，`快把[球|气球|娃娃|玩具车|糖果|巧克力|饼干|汉堡包|披萨|意大利面|酸奶|可乐|果汁|柠檬汁]放在咕噜咕噜魔法盒上吧！`</t>
-  </si>
-  <si>
-    <t>{user_name}，时间快来不及了！`赶紧把[球|气球|娃娃|玩具车|糖果|巧克力|饼干|汉堡包|披萨|意大利面|酸奶|可乐|果汁|柠檬汁]放在咕噜咕噜魔法盒上吧！`</t>
+    <t>{user_name}，请先把[球|气球|娃娃|玩具车|糖果|巧克力|饼干|汉堡包|披萨|意大利面|酸奶|可乐|果汁|柠檬汁]放在咕噜咕噜魔法盒上，激发它魔法力量吧！</t>
+  </si>
+  <si>
+    <t>{user_name}，快把[球|气球|娃娃|玩具车|糖果|巧克力|饼干|汉堡包|披萨|意大利面|酸奶|可乐|果汁|柠檬汁]放在咕噜咕噜魔法盒上吧！</t>
+  </si>
+  <si>
+    <t>{user_name}，时间快来不及了！赶紧把[球|气球|娃娃|玩具车|糖果|巧克力|饼干|汉堡包|披萨|意大利面|酸奶|可乐|果汁|柠檬汁]放在咕噜咕噜魔法盒上吧！</t>
   </si>
   <si>
     <t>[200525|200526|200527|200528|200529|200530|200531|200532|200533|200534|200535|200536|200537|200538]|200520</t>
@@ -130,7 +130,7 @@
     <t>{user_name}，我来帮你制造神奇道具吧！大声读出它们的英文名字吧！</t>
   </si>
   <si>
-    <t>`跟我一起读吧！[{word_en}]`</t>
+    <t>跟我一起读吧！[{word_en}]</t>
   </si>
   <si>
     <t>魔法成功了！让我们看看神奇道具的超能力吧！</t>
